--- a/output/graficos_regionales_migracion/plot_migracion_nacionalidad_2022_tarapaca.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_nacionalidad_2022_tarapaca.xlsx
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20 17:26</t>
+    <t xml:space="preserve">2026-09-08 10:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
